--- a/data/import.xlsx
+++ b/data/import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plaisancem\Documents\Dev\Apps\cfpicks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FB4988-BD11-4521-BF48-B762B913F613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DF608D-BF4F-40AE-8803-9A680831B9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2385" yWindow="1050" windowWidth="27285" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>date</t>
   </si>
@@ -47,91 +47,37 @@
     <t>Texas</t>
   </si>
   <si>
-    <t>Kansas</t>
-  </si>
-  <si>
-    <t>LSU</t>
-  </si>
-  <si>
-    <t>Missouri</t>
-  </si>
-  <si>
     <t>Arizona St</t>
   </si>
   <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
-    <t>Notre Dame</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>OU</t>
-  </si>
-  <si>
-    <t>Texas A&amp;M</t>
-  </si>
-  <si>
-    <t>Auburn</t>
-  </si>
-  <si>
-    <t>Vanderbilt</t>
-  </si>
-  <si>
-    <t>Louisville</t>
-  </si>
-  <si>
-    <t>Minnesota</t>
-  </si>
-  <si>
-    <t>Wisconsin</t>
-  </si>
-  <si>
-    <t>Georgia Tech</t>
-  </si>
-  <si>
     <t>Georgia</t>
   </si>
   <si>
-    <t>Tennessee</t>
-  </si>
-  <si>
-    <t>S Carolina</t>
-  </si>
-  <si>
     <t>Clemson</t>
   </si>
   <si>
-    <t>Baylor</t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t>Texas Tech</t>
-  </si>
-  <si>
-    <t>USC</t>
-  </si>
-  <si>
-    <t>Miami</t>
-  </si>
-  <si>
-    <t>Syracuse</t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t>Kansas St</t>
-  </si>
-  <si>
     <t>Iowa St</t>
+  </si>
+  <si>
+    <t>UNLV</t>
+  </si>
+  <si>
+    <t>Boise St</t>
+  </si>
+  <si>
+    <t>Tulane</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>Penn St</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>SMU</t>
   </si>
 </sst>
 </file>
@@ -510,168 +456,96 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>45625.458333333336</v>
+        <v>45632.791666666664</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>45625.770833333336</v>
+        <v>45632.791666666664</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>45626.458333333336</v>
+        <v>45633.458333333336</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>45626.458333333336</v>
+        <v>45633.625</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>45626.458333333336</v>
+        <v>45633.791666666664</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>45626.458333333336</v>
+        <v>45633.791666666664</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>45626.458333333336</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
+      <c r="A8"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>45626.604166666664</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
+      <c r="A9"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>45626.604166666664</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
+      <c r="A10"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>45626.604166666664</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
+      <c r="A11"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>45626.604166666664</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
+      <c r="A12"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>45626.604166666664</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
+      <c r="A13"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>45626.75</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
+      <c r="A14"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>45626.770833333336</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
+      <c r="A15"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>45626.770833333336</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
+      <c r="A16"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17"/>
